--- a/examples/entrada_malvinas.xlsx
+++ b/examples/entrada_malvinas.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,27 +1106,9 @@
           <t>MALV</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3070</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5400</v>
-      </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" t="n">
-        <v>420</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="J2" t="n">
-        <v>230</v>
-      </c>
       <c r="K2" t="n">
         <v>3400</v>
       </c>
@@ -1135,19 +1117,16 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OB1954</t>
+          <t>OB2145</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Airbus H125</t>
+          <t>Airbus H145</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1155,37 +1134,38 @@
           <t>MALV</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1265</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G3" t="n">
-        <v>600</v>
-      </c>
-      <c r="H3" t="n">
-        <v>195</v>
-      </c>
-      <c r="I3" t="n">
-        <v>540</v>
-      </c>
-      <c r="J3" t="n">
-        <v>220</v>
-      </c>
       <c r="K3" t="n">
-        <v>1800</v>
+        <v>2600</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>1</v>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OB1171</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mi-171</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MALV</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>5200</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/examples/entrada_malvinas.xlsx
+++ b/examples/entrada_malvinas.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,22 +458,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Regreso a base</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
+          <t>Altitud de crucero (m)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Regreso a base</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1020,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1087,6 +1097,11 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tamaño (1-3)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Vel. vertical (m/s)</t>
         </is>
       </c>
     </row>

--- a/examples/entrada_malvinas.xlsx
+++ b/examples/entrada_malvinas.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,22 +468,52 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Regreso a base</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
+          <t>Minutos base por parada</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>Minutos por pax</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Minutos por 100 kg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Regreso a base</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>Hora inicio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1030,7 +1060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,6 +1134,11 @@
           <t>Vel. vertical (m/s)</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>T. tierra admisible (min)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1132,6 +1167,9 @@
           <t>SI</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1157,6 +1195,9 @@
           <t>SI</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1181,6 +1222,9 @@
         <is>
           <t>SI</t>
         </is>
+      </c>
+      <c r="O4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
